--- a/assets/template_metadata.xlsx
+++ b/assets/template_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\jean_nascimento\MK-Viral-Assembly\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025222D6-B051-467C-B3CB-38844E3A8FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECE069C-5984-4415-A9FE-8C543AB1222B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
